--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotCacheWithoutSourceData-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotCacheWithoutSourceData-output.xlsx
@@ -599,13 +599,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{EC7C4235-352F-4BDF-B9D1-DCFA145DE1A0}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A3:C20"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="2" width="15.855469" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="1" max="2" width="15.855469" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -699,36 +696,29 @@
       <x:c r="C20" s="10"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{C9FE76AD-456E-41D6-93C4-9F5F282D74AF}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:B4"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="9.710938" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="1" max="1" width="9.140625"/>
+    <x:col min="2" max="2" width="9.710938" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A2" s="0">
+      <x:c r="A2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="1">
@@ -736,7 +726,7 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A3" s="0">
+      <x:c r="A3">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="1">
@@ -744,7 +734,7 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A4" s="0">
+      <x:c r="A4">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="1">
@@ -752,10 +742,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotCacheWithoutSourceData-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotCacheWithoutSourceData-output.xlsx
@@ -602,7 +602,7 @@
   <x:dimension ref="A3:C20"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="2" width="15.855469" bestFit="1" customWidth="1"/>
+    <x:col min="1" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -705,8 +705,7 @@
   <x:dimension ref="A1:B4"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="9.710938" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2" x14ac:dyDescent="0.25">
